--- a/docs/授权客户导入模板（证件自动识别版）.xlsx
+++ b/docs/授权客户导入模板（证件自动识别版）.xlsx
@@ -1,28 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView windowHeight="18160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="18160"/>
   </bookViews>
   <sheets>
-    <sheet name="代理信息" sheetId="3" r:id="rId1"/>
+    <sheet sheetId="3" name="代理信息" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -116,7 +103,7 @@
     <t>公司 / 个人，下拉选择</t>
   </si>
   <si>
-    <t>PNG/JPG格式，插入图片后拖到本列对应行；
+    <t xml:space="preserve">PNG/JPG格式，插入图片后拖到本列对应行；
 个人客户留空</t>
   </si>
   <si>
@@ -141,7 +128,7 @@
     <t/>
   </si>
   <si>
-    <t>多个用英文逗号,分隔；
+    <t xml:space="preserve">多个用英文逗号,分隔；
 无品牌填店铺名称</t>
   </si>
   <si>
@@ -223,212 +210,62 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <color rgb="FF1F1F1F"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
+    </font>
+    <font>
       <charset val="134"/>
+      <color theme="1"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="宋体"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <color rgb="FFC00000"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <scheme val="minor"/>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="134"/>
+      <color rgb="FFC00000"/>
+      <scheme val="minor"/>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
+      <charset val="134"/>
+      <color rgb="FF808080"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,194 +302,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -675,353 +326,62 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="00FFF2CC"/>
-    </mruColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1309,11 +669,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.6923076923077" customWidth="1"/>
     <col min="2" max="4" width="20.6923076923077" customWidth="1"/>
@@ -1337,7 +696,7 @@
     <col min="24" max="24" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:24">
+    <row r="1" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +730,7 @@
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:24">
+    <row r="2" ht="30" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
@@ -1445,7 +804,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" spans="1:24">
+    <row r="3" ht="42" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>28</v>
       </c>
@@ -1515,7 +874,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>42</v>
       </c>
@@ -1594,24 +953,44 @@
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="R1:X1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="A10:A200">
+      <formula1>"企业,个人"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="A4:A200">
-      <formula1>#REF!</formula1>
+      <formula1>"企业,个人"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="H10:H200">
+      <formula1>"英国,欧盟,美国,土耳其,加拿大"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="H4:H200">
-      <formula1>#REF!</formula1>
+      <formula1>"英国,欧盟,美国,土耳其,加拿大"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="I10:I200">
+      <formula1>"OVERSEA WALKERS LIMITED（英国）,Oversea Walkers（欧盟）,EU Consulten Srls（欧盟）,Oversea Walkers LLC（美国）,OVERSEAWALKERS DANISMANLIK LiMiTED SiRKETi（土耳其）"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="I4:I200">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="L4:L200 R4:R200">
-      <formula1>#REF!</formula1>
+      <formula1>"OVERSEA WALKERS LIMITED（英国）,Oversea Walkers（欧盟）,EU Consulten Srls（欧盟）,Oversea Walkers LLC（美国）,OVERSEAWALKERS DANISMANLIK LiMiTED SiRKETi（土耳其）"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="L10:L200">
+      <formula1>"Amazon,Temu,Shein,TikTok,速卖通,阿里国际站,Fruugo,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="L4:L200">
+      <formula1>"Amazon,Temu,Shein,TikTok,速卖通,阿里国际站,Fruugo,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="R10:R200">
+      <formula1>"Amazon,Temu,Shein,TikTok,速卖通,阿里国际站,Fruugo,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="R4:R200">
+      <formula1>"Amazon,Temu,Shein,TikTok,速卖通,阿里国际站,Fruugo,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="X10:X200">
+      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入不合法" error="请从下拉列表中选择有效值" sqref="X4:X200">
-      <formula1>#REF!</formula1>
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>